--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/98.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/98.xlsx
@@ -426,13 +426,13 @@
         <v>-8.446522909278302</v>
       </c>
       <c r="E2">
-        <v>-23.56943678543566</v>
+        <v>-12.39256970441021</v>
       </c>
       <c r="F2">
-        <v>-0.8359178442872826</v>
+        <v>1.812554734455907</v>
       </c>
       <c r="G2">
-        <v>-20.77698826567984</v>
+        <v>-21.09756494297517</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.407512997645449</v>
       </c>
       <c r="E3">
-        <v>-23.73288752626851</v>
+        <v>-13.10153400962906</v>
       </c>
       <c r="F3">
-        <v>-0.6021794800805322</v>
+        <v>1.913959424221495</v>
       </c>
       <c r="G3">
-        <v>-20.39744746178456</v>
+        <v>-19.62443507836474</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.189747962158015</v>
       </c>
       <c r="E4">
-        <v>-24.06642322235546</v>
+        <v>-13.84932997946368</v>
       </c>
       <c r="F4">
-        <v>-0.4011256385566212</v>
+        <v>2.456020782722616</v>
       </c>
       <c r="G4">
-        <v>-19.35645138277904</v>
+        <v>-19.42450461215707</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.961915744553751</v>
       </c>
       <c r="E5">
-        <v>-23.6804568542077</v>
+        <v>-14.93427989611737</v>
       </c>
       <c r="F5">
-        <v>-0.4889207515378801</v>
+        <v>2.497851207067118</v>
       </c>
       <c r="G5">
-        <v>-19.67845821574733</v>
+        <v>-19.67190168030681</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.731738184130861</v>
       </c>
       <c r="E6">
-        <v>-23.99965087311235</v>
+        <v>-15.6510241196814</v>
       </c>
       <c r="F6">
-        <v>-0.4674385726479018</v>
+        <v>2.135473954319925</v>
       </c>
       <c r="G6">
-        <v>-19.25150708918414</v>
+        <v>-18.21593533904473</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.554165386901217</v>
       </c>
       <c r="E7">
-        <v>-25.53640664151132</v>
+        <v>-16.39123942402718</v>
       </c>
       <c r="F7">
-        <v>-0.488455141998741</v>
+        <v>2.398549678757234</v>
       </c>
       <c r="G7">
-        <v>-18.08952712344596</v>
+        <v>-18.22304804613585</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.43975799613529</v>
       </c>
       <c r="E8">
-        <v>-24.93905563515953</v>
+        <v>-18.20780054441208</v>
       </c>
       <c r="F8">
-        <v>-0.3018502413943417</v>
+        <v>2.766406553971847</v>
       </c>
       <c r="G8">
-        <v>-18.37519078748414</v>
+        <v>-16.29759503394926</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.4037679174222834</v>
       </c>
       <c r="E9">
-        <v>-25.58279180077189</v>
+        <v>-17.04753304806282</v>
       </c>
       <c r="F9">
-        <v>0.01041697248243131</v>
+        <v>2.843374661462204</v>
       </c>
       <c r="G9">
-        <v>-17.43931115044156</v>
+        <v>-16.17990514002816</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.5596884261042939</v>
       </c>
       <c r="E10">
-        <v>-27.29672864319497</v>
+        <v>-16.78610877207401</v>
       </c>
       <c r="F10">
-        <v>-0.4309349431499802</v>
+        <v>2.809847607232351</v>
       </c>
       <c r="G10">
-        <v>-16.80528043457865</v>
+        <v>-15.83399120244803</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>1.454651569964585</v>
       </c>
       <c r="E11">
-        <v>-27.97695978083515</v>
+        <v>-18.12567213980897</v>
       </c>
       <c r="F11">
-        <v>-0.04012304254403005</v>
+        <v>2.914635092833318</v>
       </c>
       <c r="G11">
-        <v>-16.49383258660787</v>
+        <v>-15.4443135081115</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>2.299642779296193</v>
       </c>
       <c r="E12">
-        <v>-27.30862947288713</v>
+        <v>-19.78476010505115</v>
       </c>
       <c r="F12">
-        <v>0.1523281084472139</v>
+        <v>3.034493123925606</v>
       </c>
       <c r="G12">
-        <v>-16.24814210468362</v>
+        <v>-13.9692900114526</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.108972307497728</v>
       </c>
       <c r="E13">
-        <v>-28.34659647171124</v>
+        <v>-17.98140401487261</v>
       </c>
       <c r="F13">
-        <v>0.3696521526933921</v>
+        <v>2.952316207679369</v>
       </c>
       <c r="G13">
-        <v>-15.87365319328127</v>
+        <v>-13.76697595245666</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.886326682320765</v>
       </c>
       <c r="E14">
-        <v>-28.34435487707744</v>
+        <v>-20.37851097456685</v>
       </c>
       <c r="F14">
-        <v>0.3302938932828909</v>
+        <v>3.099507419166226</v>
       </c>
       <c r="G14">
-        <v>-15.80919190581335</v>
+        <v>-12.58130903338499</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.63074299982188</v>
       </c>
       <c r="E15">
-        <v>-28.72826984649972</v>
+        <v>-22.05922240319565</v>
       </c>
       <c r="F15">
-        <v>0.5866317409029621</v>
+        <v>2.928004738171457</v>
       </c>
       <c r="G15">
-        <v>-15.01070984028714</v>
+        <v>-12.77435356487097</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.333595725141773</v>
       </c>
       <c r="E16">
-        <v>-30.40140060963968</v>
+        <v>-21.7253923562982</v>
       </c>
       <c r="F16">
-        <v>0.6923409433467144</v>
+        <v>3.175918062174349</v>
       </c>
       <c r="G16">
-        <v>-14.67850321651236</v>
+        <v>-11.71196639586346</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.973785614714556</v>
       </c>
       <c r="E17">
-        <v>-31.12744179034145</v>
+        <v>-22.19797031831666</v>
       </c>
       <c r="F17">
-        <v>1.133716614567857</v>
+        <v>3.547748455530799</v>
       </c>
       <c r="G17">
-        <v>-14.37281737305267</v>
+        <v>-11.60512515967456</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.521656074055769</v>
       </c>
       <c r="E18">
-        <v>-31.11162383063266</v>
+        <v>-24.3085063858575</v>
       </c>
       <c r="F18">
-        <v>0.8652895478422792</v>
+        <v>3.861901863152861</v>
       </c>
       <c r="G18">
-        <v>-14.19980329735205</v>
+        <v>-11.76634541689153</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.950628166719786</v>
       </c>
       <c r="E19">
-        <v>-32.47092455233005</v>
+        <v>-23.74156408246721</v>
       </c>
       <c r="F19">
-        <v>0.6987137759504427</v>
+        <v>4.024258642485966</v>
       </c>
       <c r="G19">
-        <v>-13.49434094038829</v>
+        <v>-10.78096153712746</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.237289053591482</v>
       </c>
       <c r="E20">
-        <v>-33.61735529634888</v>
+        <v>-24.60993520123006</v>
       </c>
       <c r="F20">
-        <v>1.109506502238535</v>
+        <v>3.885354964054603</v>
       </c>
       <c r="G20">
-        <v>-13.70793733858207</v>
+        <v>-10.92794313798002</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.367070835229751</v>
       </c>
       <c r="E21">
-        <v>-33.01407198904704</v>
+        <v>-24.75331121678691</v>
       </c>
       <c r="F21">
-        <v>1.473654338199189</v>
+        <v>3.826165539170969</v>
       </c>
       <c r="G21">
-        <v>-14.55355495149641</v>
+        <v>-11.84088234970822</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.339504352649303</v>
       </c>
       <c r="E22">
-        <v>-33.56303398638988</v>
+        <v>-25.68891206066764</v>
       </c>
       <c r="F22">
-        <v>1.313429227028264</v>
+        <v>4.170271576771738</v>
       </c>
       <c r="G22">
-        <v>-13.60434374756719</v>
+        <v>-10.62787529030048</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.168672981962535</v>
       </c>
       <c r="E23">
-        <v>-33.18538868923122</v>
+        <v>-25.02343921981846</v>
       </c>
       <c r="F23">
-        <v>1.602762795543559</v>
+        <v>3.833919363332961</v>
       </c>
       <c r="G23">
-        <v>-13.82053230291822</v>
+        <v>-11.05237992371014</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.875494076512803</v>
       </c>
       <c r="E24">
-        <v>-33.81084114103761</v>
+        <v>-27.04665272306939</v>
       </c>
       <c r="F24">
-        <v>1.595401730448596</v>
+        <v>4.019002322552623</v>
       </c>
       <c r="G24">
-        <v>-13.72608574922835</v>
+        <v>-11.10210100716446</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.489964479258237</v>
       </c>
       <c r="E25">
-        <v>-33.12882804887541</v>
+        <v>-27.08870866117862</v>
       </c>
       <c r="F25">
-        <v>1.665556735090733</v>
+        <v>3.851808905353765</v>
       </c>
       <c r="G25">
-        <v>-13.28548855395229</v>
+        <v>-10.5209678432008</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.045466084229788</v>
       </c>
       <c r="E26">
-        <v>-34.00916339596653</v>
+        <v>-27.35498293282964</v>
       </c>
       <c r="F26">
-        <v>1.296272940846309</v>
+        <v>3.631873330053027</v>
       </c>
       <c r="G26">
-        <v>-13.22117127521533</v>
+        <v>-10.27309736703894</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.570955669912252</v>
       </c>
       <c r="E27">
-        <v>-34.22716413469578</v>
+        <v>-26.39042249766986</v>
       </c>
       <c r="F27">
-        <v>1.333448853505334</v>
+        <v>3.602519340910357</v>
       </c>
       <c r="G27">
-        <v>-12.8880674935994</v>
+        <v>-10.81777149297861</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.08778507964381</v>
       </c>
       <c r="E28">
-        <v>-34.621668940585</v>
+        <v>-25.64477302451488</v>
       </c>
       <c r="F28">
-        <v>1.46575006197523</v>
+        <v>3.866390085717216</v>
       </c>
       <c r="G28">
-        <v>-12.2626822674123</v>
+        <v>-11.12049770872619</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.608384076556593</v>
       </c>
       <c r="E29">
-        <v>-35.36214463218622</v>
+        <v>-26.77902443769008</v>
       </c>
       <c r="F29">
-        <v>1.229849147340947</v>
+        <v>3.860161370351793</v>
       </c>
       <c r="G29">
-        <v>-12.83913431998343</v>
+        <v>-10.253207609439</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.137046394698094</v>
       </c>
       <c r="E30">
-        <v>-33.28522116296731</v>
+        <v>-26.11856914604139</v>
       </c>
       <c r="F30">
-        <v>1.222945773255547</v>
+        <v>3.592806472530967</v>
       </c>
       <c r="G30">
-        <v>-13.01487794048118</v>
+        <v>-9.5278008708739</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.670508278485207</v>
       </c>
       <c r="E31">
-        <v>-33.75647681057553</v>
+        <v>-25.85658786774965</v>
       </c>
       <c r="F31">
-        <v>1.124762341321963</v>
+        <v>3.361697851996804</v>
       </c>
       <c r="G31">
-        <v>-12.68543231168615</v>
+        <v>-9.861020521583701</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.210400738394235</v>
       </c>
       <c r="E32">
-        <v>-33.71988221211954</v>
+        <v>-26.85653379880536</v>
       </c>
       <c r="F32">
-        <v>1.06053039680357</v>
+        <v>3.418662170069245</v>
       </c>
       <c r="G32">
-        <v>-12.87958918647333</v>
+        <v>-8.836029274987792</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.760321693577051</v>
       </c>
       <c r="E33">
-        <v>-33.15952657417341</v>
+        <v>-26.1984559560107</v>
       </c>
       <c r="F33">
-        <v>1.09945155338141</v>
+        <v>3.164094113809678</v>
       </c>
       <c r="G33">
-        <v>-12.65183358500809</v>
+        <v>-10.08883902341419</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.326283683075155</v>
       </c>
       <c r="E34">
-        <v>-33.30012210668955</v>
+        <v>-24.14748743556676</v>
       </c>
       <c r="F34">
-        <v>1.558954322510673</v>
+        <v>3.316858386412967</v>
       </c>
       <c r="G34">
-        <v>-13.10150829615283</v>
+        <v>-9.685396080725365</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.916737076998564</v>
       </c>
       <c r="E35">
-        <v>-32.67650595109327</v>
+        <v>-24.65985709869062</v>
       </c>
       <c r="F35">
-        <v>1.147713407448511</v>
+        <v>3.468776960057411</v>
       </c>
       <c r="G35">
-        <v>-12.93563341190765</v>
+        <v>-9.190482764786479</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.542562279714285</v>
       </c>
       <c r="E36">
-        <v>-31.79676836257116</v>
+        <v>-23.21190923405608</v>
       </c>
       <c r="F36">
-        <v>1.097677802756117</v>
+        <v>3.776063418830127</v>
       </c>
       <c r="G36">
-        <v>-12.27538814119202</v>
+        <v>-9.0655692604987</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.210547019575872</v>
       </c>
       <c r="E37">
-        <v>-32.28896820246485</v>
+        <v>-24.63215189471169</v>
       </c>
       <c r="F37">
-        <v>1.111289755099319</v>
+        <v>3.634717665877156</v>
       </c>
       <c r="G37">
-        <v>-13.01884397403723</v>
+        <v>-10.28588931500269</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9228506917153426</v>
       </c>
       <c r="E38">
-        <v>-32.47800934991506</v>
+        <v>-23.347061540815</v>
       </c>
       <c r="F38">
-        <v>0.9808145595499251</v>
+        <v>3.558497067578887</v>
       </c>
       <c r="G38">
-        <v>-12.58328542907194</v>
+        <v>-9.607326795818272</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.6804798244175528</v>
       </c>
       <c r="E39">
-        <v>-30.93198832369639</v>
+        <v>-22.57769192080783</v>
       </c>
       <c r="F39">
-        <v>1.075173341697723</v>
+        <v>3.732756980572435</v>
       </c>
       <c r="G39">
-        <v>-13.28884875767465</v>
+        <v>-10.1735525732186</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.4806088169823091</v>
       </c>
       <c r="E40">
-        <v>-30.52942962678454</v>
+        <v>-23.10672183980591</v>
       </c>
       <c r="F40">
-        <v>1.149338289717752</v>
+        <v>3.640564708116959</v>
       </c>
       <c r="G40">
-        <v>-13.13804347672423</v>
+        <v>-11.05422389757552</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.3154992059010334</v>
       </c>
       <c r="E41">
-        <v>-30.62752090226468</v>
+        <v>-22.18217952945191</v>
       </c>
       <c r="F41">
-        <v>1.188153337999258</v>
+        <v>3.88856830335703</v>
       </c>
       <c r="G41">
-        <v>-13.72309798187916</v>
+        <v>-10.87195519181986</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.1746434222473837</v>
       </c>
       <c r="E42">
-        <v>-31.03474845587845</v>
+        <v>-21.6777482812635</v>
       </c>
       <c r="F42">
-        <v>1.150849145161081</v>
+        <v>3.838383830308585</v>
       </c>
       <c r="G42">
-        <v>-12.65422379888744</v>
+        <v>-9.831553355738649</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.05022613233932763</v>
       </c>
       <c r="E43">
-        <v>-29.9229039320932</v>
+        <v>-23.45422334973251</v>
       </c>
       <c r="F43">
-        <v>1.21484986861582</v>
+        <v>4.275747974445919</v>
       </c>
       <c r="G43">
-        <v>-13.54176284996558</v>
+        <v>-11.03865109135879</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.06563867801604226</v>
       </c>
       <c r="E44">
-        <v>-29.83021965457821</v>
+        <v>-20.70165382280619</v>
       </c>
       <c r="F44">
-        <v>1.248483031142008</v>
+        <v>3.847610500971935</v>
       </c>
       <c r="G44">
-        <v>-13.65444223321298</v>
+        <v>-10.66358283448706</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.1806388571686794</v>
       </c>
       <c r="E45">
-        <v>-28.21419294867497</v>
+        <v>-22.02664003271046</v>
       </c>
       <c r="F45">
-        <v>1.6035261417948</v>
+        <v>3.673640406160912</v>
       </c>
       <c r="G45">
-        <v>-13.82686868708038</v>
+        <v>-11.05002281528618</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.3014120965895183</v>
       </c>
       <c r="E46">
-        <v>-28.2841080588794</v>
+        <v>-20.48777852389793</v>
       </c>
       <c r="F46">
-        <v>0.8947591475167764</v>
+        <v>4.120481446496236</v>
       </c>
       <c r="G46">
-        <v>-14.37540953020992</v>
+        <v>-10.69761524263077</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.4324926514880243</v>
       </c>
       <c r="E47">
-        <v>-28.45495379776678</v>
+        <v>-21.40772443313413</v>
       </c>
       <c r="F47">
-        <v>1.420259693260148</v>
+        <v>3.966298173392714</v>
       </c>
       <c r="G47">
-        <v>-14.12077064369303</v>
+        <v>-11.54615772252906</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.5779406731227036</v>
       </c>
       <c r="E48">
-        <v>-29.30237166729614</v>
+        <v>-19.25842009961363</v>
       </c>
       <c r="F48">
-        <v>1.198065753323993</v>
+        <v>3.962343659721861</v>
       </c>
       <c r="G48">
-        <v>-14.3799300801438</v>
+        <v>-12.65670670804189</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.7392815258304778</v>
       </c>
       <c r="E49">
-        <v>-27.71886393324198</v>
+        <v>-19.89336649717711</v>
       </c>
       <c r="F49">
-        <v>1.41039320540696</v>
+        <v>3.995367095470605</v>
       </c>
       <c r="G49">
-        <v>-14.17839234407682</v>
+        <v>-12.54220486947512</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9147575388440153</v>
       </c>
       <c r="E50">
-        <v>-28.06617524726026</v>
+        <v>-20.32202278979517</v>
       </c>
       <c r="F50">
-        <v>0.965036097514402</v>
+        <v>3.926475888148989</v>
       </c>
       <c r="G50">
-        <v>-14.19129188477059</v>
+        <v>-12.11481012980967</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.101376398456737</v>
       </c>
       <c r="E51">
-        <v>-27.47261910212689</v>
+        <v>-19.95937353431291</v>
       </c>
       <c r="F51">
-        <v>1.110881158973136</v>
+        <v>3.588147209727744</v>
       </c>
       <c r="G51">
-        <v>-14.1049909283801</v>
+        <v>-11.9307106923708</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.296136247689498</v>
       </c>
       <c r="E52">
-        <v>-25.93029331069849</v>
+        <v>-18.98497272513446</v>
       </c>
       <c r="F52">
-        <v>1.218745785167801</v>
+        <v>3.72055611019989</v>
       </c>
       <c r="G52">
-        <v>-13.85408964777704</v>
+        <v>-11.5731287370375</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.494209670486639</v>
       </c>
       <c r="E53">
-        <v>-26.51206183798989</v>
+        <v>-18.73156837661325</v>
       </c>
       <c r="F53">
-        <v>1.29696343662544</v>
+        <v>3.787784426310294</v>
       </c>
       <c r="G53">
-        <v>-14.33507715390498</v>
+        <v>-12.31778298736793</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.689991570777513</v>
       </c>
       <c r="E54">
-        <v>-26.68761718984525</v>
+        <v>-19.1174758745989</v>
       </c>
       <c r="F54">
-        <v>1.252378947693989</v>
+        <v>3.716653858824247</v>
       </c>
       <c r="G54">
-        <v>-15.30961899702794</v>
+        <v>-12.49181174527634</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.880999620547761</v>
       </c>
       <c r="E55">
-        <v>-26.83313517360773</v>
+        <v>-16.89580652643582</v>
       </c>
       <c r="F55">
-        <v>1.380279037424879</v>
+        <v>3.844238791077964</v>
       </c>
       <c r="G55">
-        <v>-14.79280311180123</v>
+        <v>-12.71826630234464</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.06654766582769</v>
       </c>
       <c r="E56">
-        <v>-25.05477173147753</v>
+        <v>-17.57282244753056</v>
       </c>
       <c r="F56">
-        <v>1.211436982368048</v>
+        <v>3.690283571626265</v>
       </c>
       <c r="G56">
-        <v>-15.16522458751432</v>
+        <v>-11.63903176708777</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.245202537095188</v>
       </c>
       <c r="E57">
-        <v>-25.50495186105405</v>
+        <v>-16.72872847792282</v>
       </c>
       <c r="F57">
-        <v>1.279411223964625</v>
+        <v>3.489813325732193</v>
       </c>
       <c r="G57">
-        <v>-14.5025146156447</v>
+        <v>-11.83125197273448</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.412743120755236</v>
       </c>
       <c r="E58">
-        <v>-25.51224270420639</v>
+        <v>-17.81437125109969</v>
       </c>
       <c r="F58">
-        <v>1.175236632552934</v>
+        <v>3.9745746205068</v>
       </c>
       <c r="G58">
-        <v>-14.67476561059852</v>
+        <v>-13.32251700580904</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.564778059457307</v>
       </c>
       <c r="E59">
-        <v>-24.87589247970054</v>
+        <v>-16.69981417138385</v>
       </c>
       <c r="F59">
-        <v>1.080839841463165</v>
+        <v>3.758222971692702</v>
       </c>
       <c r="G59">
-        <v>-15.0870146044218</v>
+        <v>-13.54556501151743</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.695463600891468</v>
       </c>
       <c r="E60">
-        <v>-23.9985549824025</v>
+        <v>-15.68412726467747</v>
       </c>
       <c r="F60">
-        <v>1.098374633358911</v>
+        <v>3.350594489823658</v>
       </c>
       <c r="G60">
-        <v>-14.73644769508622</v>
+        <v>-13.46934632156679</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.799980823915432</v>
       </c>
       <c r="E61">
-        <v>-24.32079213584031</v>
+        <v>-14.85228281726049</v>
       </c>
       <c r="F61">
-        <v>1.088378281620657</v>
+        <v>3.394125814321342</v>
       </c>
       <c r="G61">
-        <v>-15.53073695468694</v>
+        <v>-13.32485094041422</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.87537070504627</v>
       </c>
       <c r="E62">
-        <v>-24.10852897367878</v>
+        <v>-16.23315492489342</v>
       </c>
       <c r="F62">
-        <v>0.9569512788160836</v>
+        <v>3.756002615999256</v>
       </c>
       <c r="G62">
-        <v>-15.16245366089795</v>
+        <v>-13.0999126132029</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.920366805233729</v>
       </c>
       <c r="E63">
-        <v>-23.33104432824987</v>
+        <v>-16.54228667455303</v>
       </c>
       <c r="F63">
-        <v>0.6527356258134047</v>
+        <v>3.070234199025243</v>
       </c>
       <c r="G63">
-        <v>-14.86755191953244</v>
+        <v>-13.95642026566868</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.934898934377892</v>
       </c>
       <c r="E64">
-        <v>-23.09185033116472</v>
+        <v>-16.9619765886359</v>
       </c>
       <c r="F64">
-        <v>0.6717923590938876</v>
+        <v>3.66842526258137</v>
       </c>
       <c r="G64">
-        <v>-15.26685171447886</v>
+        <v>-14.15275051360239</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.920954187539215</v>
       </c>
       <c r="E65">
-        <v>-23.36080093095427</v>
+        <v>-16.12632822305248</v>
       </c>
       <c r="F65">
-        <v>1.317397994052355</v>
+        <v>3.434828640054051</v>
       </c>
       <c r="G65">
-        <v>-16.14693376172979</v>
+        <v>-14.15960499814145</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.88329022072529</v>
       </c>
       <c r="E66">
-        <v>-23.76877115430529</v>
+        <v>-15.97210651224725</v>
       </c>
       <c r="F66">
-        <v>1.044276822993415</v>
+        <v>3.828924354875665</v>
       </c>
       <c r="G66">
-        <v>-14.91930236740233</v>
+        <v>-13.12376178326781</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.826066923601351</v>
       </c>
       <c r="E67">
-        <v>-23.7086194340614</v>
+        <v>-15.2915402675305</v>
       </c>
       <c r="F67">
-        <v>0.7743769097664778</v>
+        <v>3.770753252895659</v>
       </c>
       <c r="G67">
-        <v>-15.73267195621863</v>
+        <v>-13.88769168500064</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.754800473984014</v>
       </c>
       <c r="E68">
-        <v>-22.88922376169151</v>
+        <v>-15.47347623926267</v>
       </c>
       <c r="F68">
-        <v>0.8390570430589402</v>
+        <v>3.272069599418423</v>
       </c>
       <c r="G68">
-        <v>-16.18387448412975</v>
+        <v>-12.57684972854359</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.674839544029265</v>
       </c>
       <c r="E69">
-        <v>-24.46652295788115</v>
+        <v>-16.17485987899268</v>
       </c>
       <c r="F69">
-        <v>0.8344975537283901</v>
+        <v>3.441074776184544</v>
       </c>
       <c r="G69">
-        <v>-16.06241056829389</v>
+        <v>-13.81842679595524</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.590363382069627</v>
       </c>
       <c r="E70">
-        <v>-24.1326340408216</v>
+        <v>-14.91277417305495</v>
       </c>
       <c r="F70">
-        <v>0.7132474451364306</v>
+        <v>2.620450633099032</v>
       </c>
       <c r="G70">
-        <v>-15.29467188391813</v>
+        <v>-14.07984567973656</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.501924301444518</v>
       </c>
       <c r="E71">
-        <v>-23.31502711568474</v>
+        <v>-15.92208498835853</v>
       </c>
       <c r="F71">
-        <v>0.7099850109506253</v>
+        <v>3.258525746429585</v>
       </c>
       <c r="G71">
-        <v>-15.90995001457384</v>
+        <v>-13.16948703825623</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.407937978624914</v>
       </c>
       <c r="E72">
-        <v>-23.35283987364878</v>
+        <v>-17.34430659215549</v>
       </c>
       <c r="F72">
-        <v>0.7922759540227744</v>
+        <v>3.446793538245196</v>
       </c>
       <c r="G72">
-        <v>-15.96470809306615</v>
+        <v>-12.58996279942465</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.30386149507114</v>
       </c>
       <c r="E73">
-        <v>-23.87495481283715</v>
+        <v>-16.09748184362361</v>
       </c>
       <c r="F73">
-        <v>0.4595789338368325</v>
+        <v>3.620074720983003</v>
       </c>
       <c r="G73">
-        <v>-15.33754675919723</v>
+        <v>-14.12083354405828</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.181977696305239</v>
       </c>
       <c r="E74">
-        <v>-24.45312773176646</v>
+        <v>-16.15069594168775</v>
       </c>
       <c r="F74">
-        <v>0.1103543587173645</v>
+        <v>2.829010448809168</v>
       </c>
       <c r="G74">
-        <v>-15.72944417431784</v>
+        <v>-14.61791692259816</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.034365040418308</v>
       </c>
       <c r="E75">
-        <v>-25.18250639781188</v>
+        <v>-17.23666929346718</v>
       </c>
       <c r="F75">
-        <v>0.4608886586289009</v>
+        <v>2.590995286777774</v>
       </c>
       <c r="G75">
-        <v>-15.27503372777917</v>
+        <v>-14.19116277349456</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.85482415600223</v>
       </c>
       <c r="E76">
-        <v>-24.48358624794205</v>
+        <v>-16.19403343794115</v>
       </c>
       <c r="F76">
-        <v>0.5603168834120202</v>
+        <v>2.839071732489955</v>
       </c>
       <c r="G76">
-        <v>-15.44252912406583</v>
+        <v>-13.06251669079129</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.637268313223737</v>
       </c>
       <c r="E77">
-        <v>-24.14802632397367</v>
+        <v>-17.08720248037001</v>
       </c>
       <c r="F77">
-        <v>-0.142976823222245</v>
+        <v>2.725138345227326</v>
       </c>
       <c r="G77">
-        <v>-15.04189352399431</v>
+        <v>-13.30228957256409</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.377224860029174</v>
       </c>
       <c r="E78">
-        <v>-25.01488040394396</v>
+        <v>-18.31536538751628</v>
       </c>
       <c r="F78">
-        <v>0.299735495791529</v>
+        <v>2.32901548683395</v>
       </c>
       <c r="G78">
-        <v>-15.11892991869315</v>
+        <v>-13.45125750074022</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.074720932404831</v>
       </c>
       <c r="E79">
-        <v>-26.15613736640903</v>
+        <v>-17.94643061011137</v>
       </c>
       <c r="F79">
-        <v>0.201266996793166</v>
+        <v>2.912056819602982</v>
       </c>
       <c r="G79">
-        <v>-14.3200903142487</v>
+        <v>-12.58320597597899</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.7301546708462281</v>
       </c>
       <c r="E80">
-        <v>-26.30752878095945</v>
+        <v>-19.37866014146529</v>
       </c>
       <c r="F80">
-        <v>0.08790215995417944</v>
+        <v>2.671938496115884</v>
       </c>
       <c r="G80">
-        <v>-14.84486971677012</v>
+        <v>-11.95781743924635</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.3447981334060261</v>
       </c>
       <c r="E81">
-        <v>-26.39369658437741</v>
+        <v>-19.24584905576834</v>
       </c>
       <c r="F81">
-        <v>0.574133133818314</v>
+        <v>2.783903336925622</v>
       </c>
       <c r="G81">
-        <v>-14.87470766371557</v>
+        <v>-12.35210341297355</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.07613109129721174</v>
       </c>
       <c r="E82">
-        <v>-26.82788214375883</v>
+        <v>-20.4770188696557</v>
       </c>
       <c r="F82">
-        <v>0.02571477977261866</v>
+        <v>2.929425322377607</v>
       </c>
       <c r="G82">
-        <v>-14.34782606477672</v>
+        <v>-12.60046716042076</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.5221984270246185</v>
       </c>
       <c r="E83">
-        <v>-27.14592140179153</v>
+        <v>-19.066761494187</v>
       </c>
       <c r="F83">
-        <v>0.1933753902165312</v>
+        <v>2.31667366663493</v>
       </c>
       <c r="G83">
-        <v>-14.77514135134922</v>
+        <v>-11.41212697582613</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.9821368335696621</v>
       </c>
       <c r="E84">
-        <v>-28.3159341742053</v>
+        <v>-21.2705569554418</v>
       </c>
       <c r="F84">
-        <v>-0.1917201238876403</v>
+        <v>2.905870864297276</v>
       </c>
       <c r="G84">
-        <v>-14.3270192860624</v>
+        <v>-11.31645220974119</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.442350589982853</v>
       </c>
       <c r="E85">
-        <v>-28.35004716890509</v>
+        <v>-22.2599877698517</v>
       </c>
       <c r="F85">
-        <v>0.09336832092131869</v>
+        <v>2.241834059894924</v>
       </c>
       <c r="G85">
-        <v>-14.67309212982842</v>
+        <v>-12.98402365605518</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.885900111784465</v>
       </c>
       <c r="E86">
-        <v>-30.08958347489352</v>
+        <v>-22.51142223217959</v>
       </c>
       <c r="F86">
-        <v>-0.07049139532553918</v>
+        <v>2.348181495822598</v>
       </c>
       <c r="G86">
-        <v>-13.3789022174339</v>
+        <v>-11.62788847080259</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.294956851905455</v>
       </c>
       <c r="E87">
-        <v>-31.29085630338225</v>
+        <v>-23.15738640700372</v>
       </c>
       <c r="F87">
-        <v>-0.2638024986288667</v>
+        <v>1.900537516588145</v>
       </c>
       <c r="G87">
-        <v>-14.17303588139428</v>
+        <v>-10.95616222815677</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.652432774848917</v>
       </c>
       <c r="E88">
-        <v>-31.82902015445379</v>
+        <v>-25.68456925409428</v>
       </c>
       <c r="F88">
-        <v>-0.4055418025018241</v>
+        <v>2.05334138183932</v>
       </c>
       <c r="G88">
-        <v>-12.72931028226365</v>
+        <v>-10.39706074475695</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.941429265343016</v>
       </c>
       <c r="E89">
-        <v>-32.11627484618234</v>
+        <v>-27.42181415223484</v>
       </c>
       <c r="F89">
-        <v>-0.2133377096333887</v>
+        <v>2.104141916488872</v>
       </c>
       <c r="G89">
-        <v>-13.45597502813368</v>
+        <v>-10.05628311858099</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.146468820960366</v>
       </c>
       <c r="E90">
-        <v>-33.98478209190923</v>
+        <v>-27.01894751909046</v>
       </c>
       <c r="F90">
-        <v>-0.1546099350241054</v>
+        <v>2.142090677634632</v>
       </c>
       <c r="G90">
-        <v>-12.84552367287423</v>
+        <v>-8.967855198361571</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.257103305069651</v>
       </c>
       <c r="E91">
-        <v>-35.75012390703038</v>
+        <v>-29.90642028670528</v>
       </c>
       <c r="F91">
-        <v>-0.4095667910859135</v>
+        <v>1.879570833973643</v>
       </c>
       <c r="G91">
-        <v>-13.21492758632826</v>
+        <v>-10.24989706389973</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.267858831693389</v>
       </c>
       <c r="E92">
-        <v>-35.81843820167309</v>
+        <v>-30.17487728282799</v>
       </c>
       <c r="F92">
-        <v>-0.1743001506707641</v>
+        <v>1.935312531079365</v>
       </c>
       <c r="G92">
-        <v>-12.91104599018748</v>
+        <v>-9.3559140359294</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.178825766019767</v>
       </c>
       <c r="E93">
-        <v>-37.79384007635104</v>
+        <v>-33.41709259030767</v>
       </c>
       <c r="F93">
-        <v>-0.4645483093522247</v>
+        <v>1.936620672165518</v>
       </c>
       <c r="G93">
-        <v>-13.28148610439531</v>
+        <v>-9.948339470727518</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.996867908874072</v>
       </c>
       <c r="E94">
-        <v>-39.39502244445713</v>
+        <v>-36.08730955316751</v>
       </c>
       <c r="F94">
-        <v>-0.7739894000228961</v>
+        <v>1.704314769959282</v>
       </c>
       <c r="G94">
-        <v>-12.74583321505015</v>
+        <v>-10.23319205110857</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.736894230909779</v>
       </c>
       <c r="E95">
-        <v>-40.74258989000065</v>
+        <v>-37.88743231290456</v>
       </c>
       <c r="F95">
-        <v>-0.7685169042320951</v>
+        <v>2.128333024347209</v>
       </c>
       <c r="G95">
-        <v>-12.23444662450785</v>
+        <v>-9.463877547056113</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.41720822908888</v>
       </c>
       <c r="E96">
-        <v>-42.44902757946703</v>
+        <v>-39.67770790591194</v>
       </c>
       <c r="F96">
-        <v>-0.4462826371765039</v>
+        <v>1.778486052802973</v>
       </c>
       <c r="G96">
-        <v>-11.82607427951106</v>
+        <v>-9.561247312457157</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.064345083602412</v>
       </c>
       <c r="E97">
-        <v>-43.86226695506978</v>
+        <v>-40.87192310765972</v>
       </c>
       <c r="F97">
-        <v>-0.8339603837757994</v>
+        <v>1.677529551811455</v>
       </c>
       <c r="G97">
-        <v>-12.33855997117239</v>
+        <v>-9.885571527302936</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.701985598204412</v>
       </c>
       <c r="E98">
-        <v>-46.96418560931783</v>
+        <v>-44.09195342097583</v>
       </c>
       <c r="F98">
-        <v>-1.069010056480534</v>
+        <v>1.289803502181739</v>
       </c>
       <c r="G98">
-        <v>-13.06920730332616</v>
+        <v>-9.678298271089167</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.362608570117356</v>
       </c>
       <c r="E99">
-        <v>-48.25960541242602</v>
+        <v>-46.17516014788037</v>
       </c>
       <c r="F99">
-        <v>-1.21447582037252</v>
+        <v>0.9097489240064108</v>
       </c>
       <c r="G99">
-        <v>-13.00301294526844</v>
+        <v>-8.986218794467908</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.062457708020623</v>
       </c>
       <c r="E100">
-        <v>-49.74815783925034</v>
+        <v>-47.82529305577238</v>
       </c>
       <c r="F100">
-        <v>-1.239748599371103</v>
+        <v>1.48989524236202</v>
       </c>
       <c r="G100">
-        <v>-13.27188552233142</v>
+        <v>-10.6563194975739</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.8365892089911063</v>
       </c>
       <c r="E101">
-        <v>-51.56616014648818</v>
+        <v>-48.67217656536884</v>
       </c>
       <c r="F101">
-        <v>-1.366256611602321</v>
+        <v>0.926716749184429</v>
       </c>
       <c r="G101">
-        <v>-12.61204413817159</v>
+        <v>-9.404681682268404</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.6772877655153334</v>
       </c>
       <c r="E102">
-        <v>-53.86028394665549</v>
+        <v>-51.65186944191286</v>
       </c>
       <c r="F102">
-        <v>-1.647630474186617</v>
+        <v>0.7444670398474884</v>
       </c>
       <c r="G102">
-        <v>-13.16728221492707</v>
+        <v>-9.858408501153216</v>
       </c>
     </row>
   </sheetData>
